--- a/backend/uploads/info.xlsx
+++ b/backend/uploads/info.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/uploads/showcase_images/slideshow_1775358731.mp4</t>
+          <t>/uploads/showcase_images/slideshow_1777057871.mp4</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,6 +1715,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>Client Consultation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Interior Architecture</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1764,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e0c4737f-d909-4842-9c7a-ff770e746f74</t>
+          <t>d81686ba-db5a-4ccf-8f62-8f7429d3fbca</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/uploads/showcase_images/slideshow_1774723470.mp4</t>
+          <t>/uploads/showcase_images/slideshow_1777495735.mp4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Slideshow</t>
+          <t>Slideshow_8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1775,17 +1782,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2cbe93a8-7462-4dd9-9199-b0080ceb011c</t>
+          <t>819509e7-50fd-4a3b-89e7-279878f3398a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/uploads/showcase_images/slideshow_1775358731.mp4</t>
+          <t>/uploads/showcase_images/slideshow_1777057871.mp4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Slideshow</t>
+          <t>Slideshow_3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
